--- a/property_management_forms/017_property_maintenance_request--property_management_forms.xlsx
+++ b/property_management_forms/017_property_maintenance_request--property_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>townhouse</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mobile</t>
+          <t>single_family</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Single Family</t>
         </is>
       </c>
     </row>
@@ -905,29 +905,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>single_family</t>
+          <t>multi_family</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Multi Family</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>maintenance_type_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>multi_family</t>
+          <t>repair</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Multi Family</t>
+          <t>Repair</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>repair</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Repair</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>maintenance</t>
+          <t>upgrade</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Upgrade</t>
         </is>
       </c>
     </row>
@@ -973,29 +973,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>upgrade</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Upgrade</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>maintenance_type_choices</t>
+          <t>assigned_contact_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>john</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jane</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1041,29 +1041,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bob</t>
+          <t>alice</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>Alice</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>assigned_contact_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>alice</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>chatjim</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>chatjim</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>chatjim</t>
+          <t>chat-jimmy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>chatjim</t>
+          <t>chat-jimmy</t>
         </is>
       </c>
     </row>
@@ -1109,29 +1109,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>chat-jimmy</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>chat-jimmy</t>
+          <t>jim</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>maintenance_request_status_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jim</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jim</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1177,27 +1177,10 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>maintenance_request_status_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
